--- a/SOC_iomux_complex.xlsx
+++ b/SOC_iomux_complex.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="464">
   <si>
     <t>PAD Name</t>
   </si>
@@ -111,7 +111,7 @@
     <t>y</t>
   </si>
   <si>
-    <t>PRDWUW1216DGH_V</t>
+    <t>PDDW16DGZ_V</t>
   </si>
   <si>
     <t>I</t>
@@ -135,9 +135,6 @@
     <t>JTAG_TCK</t>
   </si>
   <si>
-    <t>PRDWUW1216SDGH_V</t>
-  </si>
-  <si>
     <t>jtag_tck</t>
   </si>
   <si>
@@ -330,7 +327,7 @@
     <t>EW</t>
   </si>
   <si>
-    <t>PRDWUW1216SDGH_H</t>
+    <t>PDDW16DGZ_H</t>
   </si>
   <si>
     <t>cfg4</t>
@@ -496,9 +493,6 @@
   </si>
   <si>
     <t>SDATAIN2</t>
-  </si>
-  <si>
-    <t>PRDWUW1216DGH_H</t>
   </si>
   <si>
     <t>sdatain2</t>
@@ -3155,10 +3149,10 @@
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="25" t="s">
         <v>35</v>
-      </c>
-      <c r="L5" s="25" t="s">
-        <v>36</v>
       </c>
       <c r="M5" s="27" t="s">
         <v>28</v>
@@ -3180,7 +3174,7 @@
       <c r="Z5" s="27"/>
       <c r="AA5" s="27"/>
       <c r="AB5" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC5" s="27" t="s">
         <v>28</v>
@@ -3200,10 +3194,10 @@
     </row>
     <row r="6" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A6" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>39</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>24</v>
@@ -3220,10 +3214,10 @@
       </c>
       <c r="J6" s="26"/>
       <c r="K6" s="26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M6" s="27" t="s">
         <v>28</v>
@@ -3245,7 +3239,7 @@
       <c r="Z6" s="27"/>
       <c r="AA6" s="27"/>
       <c r="AB6" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC6" s="27" t="s">
         <v>28</v>
@@ -3265,10 +3259,10 @@
     </row>
     <row r="7" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A7" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>42</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>43</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>24</v>
@@ -3285,10 +3279,10 @@
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="25" t="s">
         <v>44</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>45</v>
       </c>
       <c r="M7" s="27" t="s">
         <v>25</v>
@@ -3310,7 +3304,7 @@
       <c r="Z7" s="27"/>
       <c r="AA7" s="27"/>
       <c r="AB7" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC7" s="27" t="s">
         <v>28</v>
@@ -3330,10 +3324,10 @@
     </row>
     <row r="8" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A8" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="25" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>48</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>24</v>
@@ -3350,10 +3344,10 @@
       </c>
       <c r="J8" s="26"/>
       <c r="K8" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M8" s="27" t="s">
         <v>28</v>
@@ -3375,7 +3369,7 @@
       <c r="Z8" s="27"/>
       <c r="AA8" s="27"/>
       <c r="AB8" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AC8" s="27" t="s">
         <v>28</v>
@@ -3395,10 +3389,10 @@
     </row>
     <row r="9" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A9" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>52</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>24</v>
@@ -3415,13 +3409,13 @@
       </c>
       <c r="J9" s="26"/>
       <c r="K9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="25" t="s">
-        <v>54</v>
-      </c>
       <c r="M9" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" s="26"/>
       <c r="O9" s="27"/>
@@ -3438,10 +3432,10 @@
       <c r="Z9" s="27"/>
       <c r="AA9" s="27"/>
       <c r="AB9" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AC9" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AD9" s="26"/>
       <c r="AE9" s="27"/>
@@ -3456,10 +3450,10 @@
     </row>
     <row r="10" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A10" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>57</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>58</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>24</v>
@@ -3478,10 +3472,10 @@
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M10" s="27" t="s">
         <v>28</v>
@@ -3517,10 +3511,10 @@
     </row>
     <row r="11" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A11" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>61</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>24</v>
@@ -3539,10 +3533,10 @@
       </c>
       <c r="J11" s="26"/>
       <c r="K11" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M11" s="27" t="s">
         <v>28</v>
@@ -3578,10 +3572,10 @@
     </row>
     <row r="12" ht="15" spans="1:39">
       <c r="A12" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="25" t="s">
         <v>63</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>64</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>24</v>
@@ -3598,10 +3592,10 @@
       </c>
       <c r="J12" s="27"/>
       <c r="K12" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M12" s="27" t="s">
         <v>28</v>
@@ -3611,18 +3605,18 @@
         <v>29</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R12" s="27"/>
       <c r="S12" s="27"/>
       <c r="T12" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U12" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V12" s="27"/>
       <c r="W12" s="27"/>
@@ -3631,7 +3625,7 @@
       <c r="Z12" s="27"/>
       <c r="AA12" s="27"/>
       <c r="AB12" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AC12" s="27" t="s">
         <v>28</v>
@@ -3651,10 +3645,10 @@
     </row>
     <row r="13" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A13" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>69</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>70</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>24</v>
@@ -3671,10 +3665,10 @@
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L13" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M13" s="27" t="s">
         <v>28</v>
@@ -3696,7 +3690,7 @@
       <c r="Z13" s="27"/>
       <c r="AA13" s="27"/>
       <c r="AB13" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC13" s="27" t="s">
         <v>28</v>
@@ -3716,10 +3710,10 @@
     </row>
     <row r="14" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A14" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>73</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>74</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>24</v>
@@ -3736,10 +3730,10 @@
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M14" s="27" t="s">
         <v>28</v>
@@ -3765,7 +3759,7 @@
       <c r="AD14" s="27"/>
       <c r="AE14" s="27"/>
       <c r="AF14" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG14" s="27" t="s">
         <v>28</v>
@@ -3781,10 +3775,10 @@
     </row>
     <row r="15" s="16" customFormat="1" ht="16.95" customHeight="1" spans="1:39">
       <c r="A15" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>77</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>78</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>24</v>
@@ -3801,10 +3795,10 @@
       </c>
       <c r="J15" s="26"/>
       <c r="K15" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M15" s="27" t="s">
         <v>28</v>
@@ -3830,7 +3824,7 @@
       <c r="AD15" s="27"/>
       <c r="AE15" s="27"/>
       <c r="AF15" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG15" s="27" t="s">
         <v>28</v>
@@ -3846,10 +3840,10 @@
     </row>
     <row r="16" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A16" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="25" t="s">
         <v>81</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>82</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>24</v>
@@ -3866,10 +3860,10 @@
       </c>
       <c r="J16" s="26"/>
       <c r="K16" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M16" s="27" t="s">
         <v>28</v>
@@ -3895,7 +3889,7 @@
       <c r="AD16" s="27"/>
       <c r="AE16" s="27"/>
       <c r="AF16" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG16" s="27" t="s">
         <v>28</v>
@@ -3911,10 +3905,10 @@
     </row>
     <row r="17" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A17" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>85</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>86</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>24</v>
@@ -3931,10 +3925,10 @@
       </c>
       <c r="J17" s="26"/>
       <c r="K17" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L17" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M17" s="27" t="s">
         <v>28</v>
@@ -3960,7 +3954,7 @@
       <c r="AD17" s="27"/>
       <c r="AE17" s="27"/>
       <c r="AF17" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG17" s="27" t="s">
         <v>28</v>
@@ -3976,10 +3970,10 @@
     </row>
     <row r="18" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A18" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="25" t="s">
         <v>89</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>90</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>24</v>
@@ -3996,10 +3990,10 @@
       </c>
       <c r="J18" s="26"/>
       <c r="K18" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M18" s="27" t="s">
         <v>28</v>
@@ -4025,7 +4019,7 @@
       <c r="AD18" s="27"/>
       <c r="AE18" s="27"/>
       <c r="AF18" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG18" s="27" t="s">
         <v>28</v>
@@ -4041,10 +4035,10 @@
     </row>
     <row r="19" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A19" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>94</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>24</v>
@@ -4061,10 +4055,10 @@
       </c>
       <c r="J19" s="26"/>
       <c r="K19" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L19" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M19" s="27" t="s">
         <v>28</v>
@@ -4090,7 +4084,7 @@
       <c r="AD19" s="27"/>
       <c r="AE19" s="27"/>
       <c r="AF19" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG19" s="27" t="s">
         <v>28</v>
@@ -4106,13 +4100,13 @@
     </row>
     <row r="20" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A20" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="C20" s="25" t="s">
         <v>98</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>99</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="26"/>
@@ -4126,10 +4120,10 @@
       </c>
       <c r="J20" s="26"/>
       <c r="K20" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" s="29" t="s">
         <v>100</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>101</v>
       </c>
       <c r="M20" s="27" t="s">
         <v>28</v>
@@ -4155,7 +4149,7 @@
       <c r="AD20" s="27"/>
       <c r="AE20" s="27"/>
       <c r="AF20" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG20" s="27" t="s">
         <v>28</v>
@@ -4171,13 +4165,13 @@
     </row>
     <row r="21" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A21" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>104</v>
-      </c>
       <c r="C21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="26"/>
@@ -4191,10 +4185,10 @@
       </c>
       <c r="J21" s="26"/>
       <c r="K21" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M21" s="27" t="s">
         <v>28</v>
@@ -4220,7 +4214,7 @@
       <c r="AD21" s="27"/>
       <c r="AE21" s="27"/>
       <c r="AF21" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG21" s="27" t="s">
         <v>28</v>
@@ -4236,13 +4230,13 @@
     </row>
     <row r="22" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A22" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="25" t="s">
-        <v>108</v>
-      </c>
       <c r="C22" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="26"/>
@@ -4256,13 +4250,13 @@
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L22" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M22" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N22" s="26"/>
       <c r="O22" s="27"/>
@@ -4283,7 +4277,7 @@
       <c r="AD22" s="27"/>
       <c r="AE22" s="27"/>
       <c r="AF22" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG22" s="27" t="s">
         <v>28</v>
@@ -4299,13 +4293,13 @@
     </row>
     <row r="23" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A23" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="25" t="s">
-        <v>112</v>
-      </c>
       <c r="C23" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="26"/>
@@ -4319,13 +4313,13 @@
       </c>
       <c r="J23" s="26"/>
       <c r="K23" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M23" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N23" s="26"/>
       <c r="O23" s="27"/>
@@ -4346,7 +4340,7 @@
       <c r="AD23" s="27"/>
       <c r="AE23" s="27"/>
       <c r="AF23" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG23" s="27" t="s">
         <v>28</v>
@@ -4362,13 +4356,13 @@
     </row>
     <row r="24" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A24" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>116</v>
-      </c>
       <c r="C24" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="26"/>
@@ -4382,10 +4376,10 @@
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M24" s="27" t="s">
         <v>28</v>
@@ -4411,7 +4405,7 @@
       <c r="AD24" s="27"/>
       <c r="AE24" s="27"/>
       <c r="AF24" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG24" s="27" t="s">
         <v>28</v>
@@ -4427,13 +4421,13 @@
     </row>
     <row r="25" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A25" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>120</v>
-      </c>
       <c r="C25" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="26"/>
@@ -4447,13 +4441,13 @@
       </c>
       <c r="J25" s="26"/>
       <c r="K25" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M25" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N25" s="26"/>
       <c r="O25" s="27"/>
@@ -4474,7 +4468,7 @@
       <c r="AD25" s="27"/>
       <c r="AE25" s="27"/>
       <c r="AF25" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG25" s="27" t="s">
         <v>28</v>
@@ -4490,13 +4484,13 @@
     </row>
     <row r="26" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A26" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>124</v>
-      </c>
       <c r="C26" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="26"/>
@@ -4510,18 +4504,18 @@
       </c>
       <c r="J26" s="26"/>
       <c r="K26" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="L26" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="L26" s="25" t="s">
-        <v>126</v>
-      </c>
       <c r="M26" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="26"/>
       <c r="O26" s="27"/>
       <c r="P26" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q26" s="27" t="s">
         <v>25</v>
@@ -4543,7 +4537,7 @@
       <c r="AD26" s="27"/>
       <c r="AE26" s="27"/>
       <c r="AF26" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG26" s="27" t="s">
         <v>28</v>
@@ -4559,13 +4553,13 @@
     </row>
     <row r="27" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A27" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B27" s="25" t="s">
-        <v>130</v>
-      </c>
       <c r="C27" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="26"/>
@@ -4579,18 +4573,18 @@
       </c>
       <c r="J27" s="26"/>
       <c r="K27" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M27" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N27" s="26"/>
       <c r="O27" s="27"/>
       <c r="P27" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q27" s="27" t="s">
         <v>25</v>
@@ -4612,7 +4606,7 @@
       <c r="AD27" s="27"/>
       <c r="AE27" s="27"/>
       <c r="AF27" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG27" s="27" t="s">
         <v>28</v>
@@ -4628,13 +4622,13 @@
     </row>
     <row r="28" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A28" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="25" t="s">
-        <v>135</v>
-      </c>
       <c r="C28" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="26"/>
@@ -4648,10 +4642,10 @@
       </c>
       <c r="J28" s="26"/>
       <c r="K28" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M28" s="27" t="s">
         <v>28</v>
@@ -4661,7 +4655,7 @@
         <v>22</v>
       </c>
       <c r="P28" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q28" s="27" t="s">
         <v>25</v>
@@ -4683,7 +4677,7 @@
       <c r="AD28" s="27"/>
       <c r="AE28" s="27"/>
       <c r="AF28" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG28" s="27" t="s">
         <v>28</v>
@@ -4699,13 +4693,13 @@
     </row>
     <row r="29" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A29" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="25" t="s">
-        <v>140</v>
-      </c>
       <c r="C29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="26"/>
@@ -4719,18 +4713,18 @@
       </c>
       <c r="J29" s="26"/>
       <c r="K29" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M29" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N29" s="26"/>
       <c r="O29" s="27"/>
       <c r="P29" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q29" s="27" t="s">
         <v>25</v>
@@ -4752,7 +4746,7 @@
       <c r="AD29" s="27"/>
       <c r="AE29" s="27"/>
       <c r="AF29" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG29" s="27" t="s">
         <v>28</v>
@@ -4768,13 +4762,13 @@
     </row>
     <row r="30" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A30" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="25" t="s">
-        <v>145</v>
-      </c>
       <c r="C30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="26"/>
@@ -4788,18 +4782,18 @@
       </c>
       <c r="J30" s="26"/>
       <c r="K30" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M30" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N30" s="26"/>
       <c r="O30" s="27"/>
       <c r="P30" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q30" s="27" t="s">
         <v>25</v>
@@ -4821,7 +4815,7 @@
       <c r="AD30" s="27"/>
       <c r="AE30" s="27"/>
       <c r="AF30" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG30" s="27" t="s">
         <v>28</v>
@@ -4837,13 +4831,13 @@
     </row>
     <row r="31" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A31" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="B31" s="25" t="s">
-        <v>150</v>
-      </c>
       <c r="C31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="26"/>
@@ -4857,18 +4851,18 @@
       </c>
       <c r="J31" s="26"/>
       <c r="K31" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L31" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M31" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N31" s="26"/>
       <c r="O31" s="27"/>
       <c r="P31" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q31" s="27" t="s">
         <v>25</v>
@@ -4890,7 +4884,7 @@
       <c r="AD31" s="27"/>
       <c r="AE31" s="27"/>
       <c r="AF31" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG31" s="27" t="s">
         <v>28</v>
@@ -4906,13 +4900,13 @@
     </row>
     <row r="32" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A32" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B32" s="25" t="s">
-        <v>155</v>
-      </c>
       <c r="C32" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
@@ -4926,10 +4920,10 @@
       </c>
       <c r="J32" s="26"/>
       <c r="K32" s="26" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M32" s="27" t="s">
         <v>28</v>
@@ -4939,7 +4933,7 @@
         <v>22</v>
       </c>
       <c r="P32" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q32" s="27" t="s">
         <v>25</v>
@@ -4961,7 +4955,7 @@
       <c r="AD32" s="27"/>
       <c r="AE32" s="27"/>
       <c r="AF32" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG32" s="27" t="s">
         <v>28</v>
@@ -4977,13 +4971,13 @@
     </row>
     <row r="33" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A33" s="24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="26"/>
@@ -4997,18 +4991,18 @@
       </c>
       <c r="J33" s="26"/>
       <c r="K33" s="26" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="L33" s="25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M33" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N33" s="26"/>
       <c r="O33" s="27"/>
       <c r="P33" s="25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Q33" s="27" t="s">
         <v>25</v>
@@ -5030,7 +5024,7 @@
       <c r="AD33" s="27"/>
       <c r="AE33" s="27"/>
       <c r="AF33" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG33" s="27" t="s">
         <v>28</v>
@@ -5046,13 +5040,13 @@
     </row>
     <row r="34" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A34" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="26"/>
@@ -5066,18 +5060,18 @@
       </c>
       <c r="J34" s="26"/>
       <c r="K34" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L34" s="25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M34" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N34" s="26"/>
       <c r="O34" s="27"/>
       <c r="P34" s="25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q34" s="27" t="s">
         <v>25</v>
@@ -5099,7 +5093,7 @@
       <c r="AD34" s="27"/>
       <c r="AE34" s="27"/>
       <c r="AF34" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG34" s="27" t="s">
         <v>28</v>
@@ -5115,13 +5109,13 @@
     </row>
     <row r="35" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A35" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="26"/>
@@ -5135,18 +5129,18 @@
       </c>
       <c r="J35" s="26"/>
       <c r="K35" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M35" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N35" s="26"/>
       <c r="O35" s="27"/>
       <c r="P35" s="25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q35" s="27" t="s">
         <v>25</v>
@@ -5168,7 +5162,7 @@
       <c r="AD35" s="27"/>
       <c r="AE35" s="27"/>
       <c r="AF35" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG35" s="27" t="s">
         <v>28</v>
@@ -5184,13 +5178,13 @@
     </row>
     <row r="36" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A36" s="24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="26"/>
@@ -5204,10 +5198,10 @@
       </c>
       <c r="J36" s="26"/>
       <c r="K36" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M36" s="27" t="s">
         <v>28</v>
@@ -5217,7 +5211,7 @@
         <v>22</v>
       </c>
       <c r="P36" s="25" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q36" s="27" t="s">
         <v>25</v>
@@ -5239,7 +5233,7 @@
       <c r="AD36" s="27"/>
       <c r="AE36" s="27"/>
       <c r="AF36" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG36" s="27" t="s">
         <v>28</v>
@@ -5255,13 +5249,13 @@
     </row>
     <row r="37" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A37" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="26"/>
@@ -5275,18 +5269,18 @@
       </c>
       <c r="J37" s="26"/>
       <c r="K37" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L37" s="25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M37" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N37" s="26"/>
       <c r="O37" s="27"/>
       <c r="P37" s="25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q37" s="27" t="s">
         <v>25</v>
@@ -5308,7 +5302,7 @@
       <c r="AD37" s="27"/>
       <c r="AE37" s="27"/>
       <c r="AF37" s="25" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG37" s="27" t="s">
         <v>28</v>
@@ -5324,13 +5318,13 @@
     </row>
     <row r="38" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A38" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
@@ -5344,10 +5338,10 @@
       </c>
       <c r="J38" s="27"/>
       <c r="K38" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M38" s="27" t="s">
         <v>25</v>
@@ -5373,10 +5367,10 @@
       <c r="AD38" s="27"/>
       <c r="AE38" s="27"/>
       <c r="AF38" s="25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG38" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH38" s="27"/>
       <c r="AI38" s="27"/>
@@ -5387,13 +5381,13 @@
     </row>
     <row r="39" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A39" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
@@ -5407,10 +5401,10 @@
       </c>
       <c r="J39" s="27"/>
       <c r="K39" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L39" s="25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M39" s="27" t="s">
         <v>25</v>
@@ -5436,10 +5430,10 @@
       <c r="AD39" s="27"/>
       <c r="AE39" s="27"/>
       <c r="AF39" s="25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG39" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH39" s="27"/>
       <c r="AI39" s="27"/>
@@ -5450,13 +5444,13 @@
     </row>
     <row r="40" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A40" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="27"/>
@@ -5470,10 +5464,10 @@
       </c>
       <c r="J40" s="27"/>
       <c r="K40" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L40" s="25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M40" s="27" t="s">
         <v>25</v>
@@ -5499,10 +5493,10 @@
       <c r="AD40" s="27"/>
       <c r="AE40" s="27"/>
       <c r="AF40" s="25" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG40" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH40" s="27"/>
       <c r="AI40" s="27"/>
@@ -5513,13 +5507,13 @@
     </row>
     <row r="41" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A41" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" s="27"/>
       <c r="E41" s="27"/>
@@ -5533,10 +5527,10 @@
       </c>
       <c r="J41" s="27"/>
       <c r="K41" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L41" s="25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M41" s="27" t="s">
         <v>25</v>
@@ -5562,10 +5556,10 @@
       <c r="AD41" s="27"/>
       <c r="AE41" s="27"/>
       <c r="AF41" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG41" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH41" s="27"/>
       <c r="AI41" s="27"/>
@@ -5576,13 +5570,13 @@
     </row>
     <row r="42" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A42" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -5592,12 +5586,12 @@
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M42" s="9" t="s">
         <v>25</v>
@@ -5633,13 +5627,13 @@
     </row>
     <row r="43" s="16" customFormat="1" ht="15" spans="1:39">
       <c r="A43" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
@@ -5649,12 +5643,12 @@
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M43" s="9" t="s">
         <v>25</v>
@@ -5690,13 +5684,13 @@
     </row>
     <row r="44" ht="15" spans="1:39">
       <c r="A44" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
@@ -5710,10 +5704,10 @@
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M44" s="9" t="s">
         <v>25</v>
@@ -5749,13 +5743,13 @@
     </row>
     <row r="45" ht="15" spans="1:39">
       <c r="A45" s="30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
@@ -5769,10 +5763,10 @@
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M45" s="9" t="s">
         <v>25</v>
@@ -5808,13 +5802,13 @@
     </row>
     <row r="46" ht="15" spans="1:39">
       <c r="A46" s="31" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D46" s="33"/>
       <c r="E46" s="33"/>
@@ -5828,10 +5822,10 @@
       </c>
       <c r="J46" s="33"/>
       <c r="K46" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L46" s="32" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M46" s="33" t="s">
         <v>25</v>
@@ -5845,10 +5839,10 @@
       <c r="R46" s="33"/>
       <c r="S46" s="33"/>
       <c r="T46" s="32" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U46" s="33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V46" s="33"/>
       <c r="W46" s="33"/>
@@ -5871,13 +5865,13 @@
     </row>
     <row r="47" ht="15" spans="1:39">
       <c r="A47" s="31" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="33"/>
       <c r="E47" s="33"/>
@@ -5891,10 +5885,10 @@
       </c>
       <c r="J47" s="33"/>
       <c r="K47" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L47" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M47" s="33" t="s">
         <v>25</v>
@@ -5908,10 +5902,10 @@
       <c r="R47" s="33"/>
       <c r="S47" s="33"/>
       <c r="T47" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="U47" s="33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V47" s="33"/>
       <c r="W47" s="33"/>
@@ -5934,13 +5928,13 @@
     </row>
     <row r="48" ht="15" spans="1:39">
       <c r="A48" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="27"/>
@@ -5954,13 +5948,13 @@
       </c>
       <c r="J48" s="27"/>
       <c r="K48" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L48" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M48" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N48" s="27"/>
       <c r="O48" s="27"/>
@@ -5981,10 +5975,10 @@
       <c r="AD48" s="27"/>
       <c r="AE48" s="27"/>
       <c r="AF48" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG48" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH48" s="27"/>
       <c r="AI48" s="27"/>
@@ -5995,13 +5989,13 @@
     </row>
     <row r="49" ht="15" spans="1:39">
       <c r="A49" s="24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="27"/>
@@ -6015,10 +6009,10 @@
       </c>
       <c r="J49" s="27"/>
       <c r="K49" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L49" s="25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M49" s="27" t="s">
         <v>25</v>
@@ -6044,10 +6038,10 @@
       <c r="AD49" s="27"/>
       <c r="AE49" s="27"/>
       <c r="AF49" s="25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG49" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH49" s="27"/>
       <c r="AI49" s="27"/>
@@ -6058,42 +6052,42 @@
     </row>
     <row r="50" ht="15" spans="1:39">
       <c r="B50" s="18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F50" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>26</v>
       </c>
       <c r="K50" t="s">
+        <v>231</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="M50" s="17" t="s">
         <v>233</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="M50" s="17" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="51" ht="15" spans="1:39">
       <c r="B51" s="18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F51" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I51" s="17" t="s">
         <v>26</v>
       </c>
       <c r="M51" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -6139,42 +6133,42 @@
   <sheetData>
     <row r="1" ht="15.6" spans="1:8">
       <c r="A1" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -6184,13 +6178,13 @@
     <row r="3" spans="1:8">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -6200,19 +6194,19 @@
     <row r="4" spans="1:8">
       <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>247</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>22</v>
@@ -6222,13 +6216,13 @@
     <row r="5" spans="1:8">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -6238,17 +6232,17 @@
     <row r="6" spans="1:8">
       <c r="A6" s="7"/>
       <c r="B6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
@@ -6257,16 +6251,16 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -6276,13 +6270,13 @@
     <row r="8" spans="1:8">
       <c r="A8" s="7"/>
       <c r="B8" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -6292,14 +6286,14 @@
     <row r="9" spans="1:8">
       <c r="A9" s="7"/>
       <c r="B9" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="10"/>
@@ -6308,14 +6302,14 @@
     <row r="10" spans="1:8">
       <c r="A10" s="7"/>
       <c r="B10" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="10"/>
@@ -6323,16 +6317,16 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -6341,16 +6335,16 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
@@ -6359,16 +6353,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -6378,13 +6372,13 @@
     <row r="14" spans="1:8">
       <c r="A14" s="7"/>
       <c r="B14" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -6394,13 +6388,13 @@
     <row r="15" spans="1:8">
       <c r="A15" s="7"/>
       <c r="B15" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -6410,13 +6404,13 @@
     <row r="16" spans="1:8">
       <c r="A16" s="7"/>
       <c r="B16" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -6426,13 +6420,13 @@
     <row r="17" spans="1:8">
       <c r="A17" s="7"/>
       <c r="B17" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -6442,13 +6436,13 @@
     <row r="18" spans="1:8">
       <c r="A18" s="7"/>
       <c r="B18" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -6458,13 +6452,13 @@
     <row r="19" spans="1:8">
       <c r="A19" s="7"/>
       <c r="B19" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6473,18 +6467,18 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G20" s="10">
         <v>1</v>
@@ -6496,15 +6490,15 @@
     <row r="21" spans="1:8">
       <c r="A21" s="13"/>
       <c r="B21" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G21" s="10">
         <v>1</v>
@@ -6516,13 +6510,13 @@
     <row r="22" spans="1:8">
       <c r="A22" s="13"/>
       <c r="B22" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -6532,15 +6526,15 @@
     <row r="23" spans="1:8">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G23" s="10">
         <v>1</v>
@@ -6552,15 +6546,15 @@
     <row r="24" spans="1:8">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G24" s="10">
         <v>1</v>
@@ -6572,15 +6566,15 @@
     <row r="25" spans="1:8">
       <c r="A25" s="13"/>
       <c r="B25" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G25" s="10">
         <v>1</v>
@@ -6592,13 +6586,13 @@
     <row r="26" spans="1:8">
       <c r="A26" s="13"/>
       <c r="B26" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -6608,15 +6602,15 @@
     <row r="27" spans="1:8">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G27" s="10">
         <v>1</v>
@@ -6628,15 +6622,15 @@
     <row r="28" spans="1:8">
       <c r="A28" s="13"/>
       <c r="B28" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G28" s="10">
         <v>1</v>
@@ -6648,15 +6642,15 @@
     <row r="29" spans="1:8">
       <c r="A29" s="13"/>
       <c r="B29" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G29" s="10">
         <v>1</v>
@@ -6668,13 +6662,13 @@
     <row r="30" spans="1:8">
       <c r="A30" s="13"/>
       <c r="B30" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -6684,15 +6678,15 @@
     <row r="31" spans="1:8">
       <c r="A31" s="13"/>
       <c r="B31" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G31" s="10">
         <v>1</v>
@@ -6704,15 +6698,15 @@
     <row r="32" spans="1:8">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G32" s="10">
         <v>1</v>
@@ -6724,15 +6718,15 @@
     <row r="33" spans="1:8">
       <c r="A33" s="13"/>
       <c r="B33" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G33" s="10">
         <v>1</v>
@@ -6744,13 +6738,13 @@
     <row r="34" spans="1:8">
       <c r="A34" s="13"/>
       <c r="B34" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -6760,15 +6754,15 @@
     <row r="35" spans="1:8">
       <c r="A35" s="13"/>
       <c r="B35" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G35" s="10">
         <v>1</v>
@@ -6779,20 +6773,20 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G36" s="10">
         <v>1</v>
@@ -6804,17 +6798,17 @@
     <row r="37" spans="1:8">
       <c r="A37" s="7"/>
       <c r="B37" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G37" s="10">
         <v>1</v>
@@ -6825,20 +6819,20 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G38" s="10">
         <v>1</v>
@@ -6850,17 +6844,17 @@
     <row r="39" spans="1:8">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G39" s="10">
         <v>1</v>
@@ -6872,17 +6866,17 @@
     <row r="40" spans="1:8">
       <c r="A40" s="7"/>
       <c r="B40" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G40" s="10">
         <v>1</v>
@@ -6894,17 +6888,17 @@
     <row r="41" spans="1:8">
       <c r="A41" s="7"/>
       <c r="B41" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G41" s="10">
         <v>1</v>
@@ -6916,17 +6910,17 @@
     <row r="42" spans="1:8">
       <c r="A42" s="7"/>
       <c r="B42" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G42" s="10">
         <v>1</v>
@@ -6938,17 +6932,17 @@
     <row r="43" spans="1:8">
       <c r="A43" s="7"/>
       <c r="B43" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G43" s="10">
         <v>1</v>
@@ -6960,17 +6954,17 @@
     <row r="44" spans="1:8">
       <c r="A44" s="7"/>
       <c r="B44" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G44" s="10">
         <v>1</v>
@@ -6982,17 +6976,17 @@
     <row r="45" spans="1:8">
       <c r="A45" s="7"/>
       <c r="B45" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G45" s="10">
         <v>1</v>
@@ -7004,17 +6998,17 @@
     <row r="46" spans="1:8">
       <c r="A46" s="7"/>
       <c r="B46" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G46" s="10">
         <v>1</v>
@@ -7026,17 +7020,17 @@
     <row r="47" spans="1:8">
       <c r="A47" s="7"/>
       <c r="B47" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G47" s="10">
         <v>1</v>
@@ -7047,16 +7041,16 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
@@ -7066,19 +7060,19 @@
     <row r="49" spans="1:8">
       <c r="A49" s="7"/>
       <c r="B49" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" s="8" t="s">
+      <c r="F49" s="8" t="s">
         <v>298</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>22</v>
@@ -7089,17 +7083,17 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="10"/>
@@ -7108,13 +7102,13 @@
     <row r="51" spans="1:8">
       <c r="A51" s="7"/>
       <c r="B51" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
@@ -7124,14 +7118,14 @@
     <row r="52" spans="1:8">
       <c r="A52" s="7"/>
       <c r="B52" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="10"/>
@@ -7140,13 +7134,13 @@
     <row r="53" spans="1:8">
       <c r="A53" s="7"/>
       <c r="B53" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
@@ -7156,14 +7150,14 @@
     <row r="54" spans="1:8">
       <c r="A54" s="7"/>
       <c r="B54" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="10"/>
@@ -7172,13 +7166,13 @@
     <row r="55" spans="1:8">
       <c r="A55" s="7"/>
       <c r="B55" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -7188,14 +7182,14 @@
     <row r="56" spans="1:8">
       <c r="A56" s="7"/>
       <c r="B56" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="10"/>
@@ -7204,13 +7198,13 @@
     <row r="57" spans="1:8">
       <c r="A57" s="7"/>
       <c r="B57" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -7220,14 +7214,14 @@
     <row r="58" spans="1:8">
       <c r="A58" s="7"/>
       <c r="B58" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="10"/>
@@ -7236,13 +7230,13 @@
     <row r="59" spans="1:8">
       <c r="A59" s="7"/>
       <c r="B59" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -7252,14 +7246,14 @@
     <row r="60" spans="1:8">
       <c r="A60" s="7"/>
       <c r="B60" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="10"/>
@@ -7268,13 +7262,13 @@
     <row r="61" spans="1:8">
       <c r="A61" s="7"/>
       <c r="B61" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -7283,22 +7277,22 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="8" t="s">
+      <c r="F62" s="8" t="s">
         <v>315</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="G62" s="10">
         <v>1</v>
@@ -7310,19 +7304,19 @@
     <row r="63" spans="1:8">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D63" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="G63" s="10">
         <v>1</v>
@@ -7334,19 +7328,19 @@
     <row r="64" spans="1:8">
       <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>321</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="G64" s="10">
         <v>1</v>
@@ -7358,19 +7352,19 @@
     <row r="65" spans="1:8">
       <c r="A65" s="7"/>
       <c r="B65" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>324</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="G65" s="10">
         <v>1</v>
@@ -7382,19 +7376,19 @@
     <row r="66" spans="1:8">
       <c r="A66" s="7"/>
       <c r="B66" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>327</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>329</v>
       </c>
       <c r="G66" s="10">
         <v>1</v>
@@ -7406,19 +7400,19 @@
     <row r="67" spans="1:8">
       <c r="A67" s="7"/>
       <c r="B67" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D67" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>332</v>
       </c>
       <c r="G67" s="10">
         <v>1</v>
@@ -7430,19 +7424,19 @@
     <row r="68" spans="1:8">
       <c r="A68" s="7"/>
       <c r="B68" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D68" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>333</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>335</v>
       </c>
       <c r="G68" s="10">
         <v>1</v>
@@ -7454,19 +7448,19 @@
     <row r="69" spans="1:8">
       <c r="A69" s="7"/>
       <c r="B69" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D69" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>336</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="G69" s="10">
         <v>1</v>
@@ -7478,19 +7472,19 @@
     <row r="70" spans="1:8">
       <c r="A70" s="7"/>
       <c r="B70" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="G70" s="10">
         <v>1</v>
@@ -7502,19 +7496,19 @@
     <row r="71" spans="1:8">
       <c r="A71" s="7"/>
       <c r="B71" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D71" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>344</v>
       </c>
       <c r="G71" s="10">
         <v>1</v>
@@ -7526,19 +7520,19 @@
     <row r="72" spans="1:8">
       <c r="A72" s="7"/>
       <c r="B72" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D72" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>345</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>347</v>
       </c>
       <c r="G72" s="10">
         <v>1</v>
@@ -7550,19 +7544,19 @@
     <row r="73" spans="1:8">
       <c r="A73" s="7"/>
       <c r="B73" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D73" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>348</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>350</v>
       </c>
       <c r="G73" s="10">
         <v>1</v>
@@ -7574,19 +7568,19 @@
     <row r="74" spans="1:8">
       <c r="A74" s="7"/>
       <c r="B74" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="E74" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D74" s="8" t="s">
+      <c r="F74" s="8" t="s">
         <v>352</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>354</v>
       </c>
       <c r="G74" s="10">
         <v>1</v>
@@ -7598,19 +7592,19 @@
     <row r="75" spans="1:8">
       <c r="A75" s="7"/>
       <c r="B75" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E75" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D75" s="8" t="s">
+      <c r="F75" s="8" t="s">
         <v>356</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>358</v>
       </c>
       <c r="G75" s="10">
         <v>1</v>
@@ -7622,19 +7616,19 @@
     <row r="76" spans="1:8">
       <c r="A76" s="7"/>
       <c r="B76" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E76" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="8" t="s">
+      <c r="F76" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="G76" s="10">
         <v>1</v>
@@ -7646,19 +7640,19 @@
     <row r="77" spans="1:8">
       <c r="A77" s="7"/>
       <c r="B77" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D77" s="8" t="s">
+      <c r="F77" s="8" t="s">
         <v>364</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>366</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -7669,17 +7663,17 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="10"/>
@@ -7688,14 +7682,14 @@
     <row r="79" spans="1:8">
       <c r="A79" s="7"/>
       <c r="B79" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="10"/>
@@ -7703,17 +7697,17 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="10"/>
@@ -7722,14 +7716,14 @@
     <row r="81" spans="1:8">
       <c r="A81" s="7"/>
       <c r="B81" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="10"/>
@@ -7738,14 +7732,14 @@
     <row r="82" spans="1:8">
       <c r="A82" s="7"/>
       <c r="B82" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="10"/>
@@ -7754,14 +7748,14 @@
     <row r="83" spans="1:8">
       <c r="A83" s="7"/>
       <c r="B83" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F83" s="8"/>
       <c r="G83" s="10"/>
@@ -7770,14 +7764,14 @@
     <row r="84" spans="1:8">
       <c r="A84" s="7"/>
       <c r="B84" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="10"/>
@@ -7786,14 +7780,14 @@
     <row r="85" spans="1:8">
       <c r="A85" s="7"/>
       <c r="B85" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="10"/>
@@ -7802,14 +7796,14 @@
     <row r="86" spans="1:8">
       <c r="A86" s="7"/>
       <c r="B86" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="10"/>
@@ -7818,14 +7812,14 @@
     <row r="87" spans="1:8">
       <c r="A87" s="7"/>
       <c r="B87" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="10"/>
@@ -7834,14 +7828,14 @@
     <row r="88" spans="1:8">
       <c r="A88" s="7"/>
       <c r="B88" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="10"/>
@@ -7850,14 +7844,14 @@
     <row r="89" spans="1:8">
       <c r="A89" s="7"/>
       <c r="B89" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="10"/>
@@ -7866,14 +7860,14 @@
     <row r="90" spans="1:8">
       <c r="A90" s="7"/>
       <c r="B90" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="10"/>
@@ -7882,14 +7876,14 @@
     <row r="91" spans="1:8">
       <c r="A91" s="7"/>
       <c r="B91" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="10"/>
@@ -7898,14 +7892,14 @@
     <row r="92" spans="1:8">
       <c r="A92" s="7"/>
       <c r="B92" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="10"/>
@@ -7914,14 +7908,14 @@
     <row r="93" spans="1:8">
       <c r="A93" s="7"/>
       <c r="B93" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="10"/>
@@ -7930,14 +7924,14 @@
     <row r="94" spans="1:8">
       <c r="A94" s="7"/>
       <c r="B94" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="10"/>
@@ -7946,14 +7940,14 @@
     <row r="95" spans="1:8">
       <c r="A95" s="7"/>
       <c r="B95" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="10"/>
@@ -7961,16 +7955,16 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -7980,14 +7974,14 @@
     <row r="97" spans="1:8">
       <c r="A97" s="7"/>
       <c r="B97" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="10"/>
@@ -7996,19 +7990,19 @@
     <row r="98" spans="1:8">
       <c r="A98" s="7"/>
       <c r="B98" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C98" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D98" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>386</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>388</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>22</v>
@@ -8020,13 +8014,13 @@
     <row r="99" spans="1:8">
       <c r="A99" s="7"/>
       <c r="B99" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -8036,13 +8030,13 @@
     <row r="100" spans="1:8">
       <c r="A100" s="7"/>
       <c r="B100" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -8052,13 +8046,13 @@
     <row r="101" spans="1:8">
       <c r="A101" s="7"/>
       <c r="B101" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
@@ -8068,13 +8062,13 @@
     <row r="102" spans="1:8">
       <c r="A102" s="7"/>
       <c r="B102" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C102" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
@@ -8084,13 +8078,13 @@
     <row r="103" spans="1:8">
       <c r="A103" s="7"/>
       <c r="B103" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
@@ -8100,13 +8094,13 @@
     <row r="104" spans="1:8">
       <c r="A104" s="7"/>
       <c r="B104" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
@@ -8116,14 +8110,14 @@
     <row r="105" spans="1:8">
       <c r="A105" s="7"/>
       <c r="B105" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F105" s="8"/>
       <c r="G105" s="10"/>
@@ -8132,14 +8126,14 @@
     <row r="106" spans="1:8">
       <c r="A106" s="7"/>
       <c r="B106" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="10"/>
@@ -8148,14 +8142,14 @@
     <row r="107" spans="1:8">
       <c r="A107" s="7"/>
       <c r="B107" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="10"/>
@@ -8164,14 +8158,14 @@
     <row r="108" spans="1:8">
       <c r="A108" s="7"/>
       <c r="B108" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="10"/>
@@ -8180,14 +8174,14 @@
     <row r="109" spans="1:8">
       <c r="A109" s="7"/>
       <c r="B109" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="10"/>
@@ -8196,14 +8190,14 @@
     <row r="110" spans="1:8">
       <c r="A110" s="7"/>
       <c r="B110" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="10"/>
@@ -8211,17 +8205,17 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F111" s="8"/>
       <c r="G111" s="10"/>
@@ -8230,14 +8224,14 @@
     <row r="112" spans="1:8">
       <c r="A112" s="7"/>
       <c r="B112" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F112" s="8"/>
       <c r="G112" s="10"/>
@@ -8246,19 +8240,19 @@
     <row r="113" spans="1:8">
       <c r="A113" s="7"/>
       <c r="B113" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="E113" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C113" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D113" s="8" t="s">
+      <c r="F113" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>407</v>
       </c>
       <c r="G113" s="10">
         <v>1</v>
@@ -8268,19 +8262,19 @@
     <row r="114" spans="1:8">
       <c r="A114" s="7"/>
       <c r="B114" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="E114" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="C114" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D114" s="8" t="s">
+      <c r="F114" s="8" t="s">
         <v>409</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>411</v>
       </c>
       <c r="G114" s="10">
         <v>1</v>
@@ -8290,19 +8284,19 @@
     <row r="115" spans="1:8">
       <c r="A115" s="7"/>
       <c r="B115" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="E115" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="C115" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D115" s="8" t="s">
+      <c r="F115" s="8" t="s">
         <v>413</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="G115" s="10">
         <v>1</v>
@@ -8312,19 +8306,19 @@
     <row r="116" spans="1:8">
       <c r="A116" s="7"/>
       <c r="B116" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="E116" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="C116" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D116" s="8" t="s">
+      <c r="F116" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="G116" s="10">
         <v>1</v>
@@ -8334,14 +8328,14 @@
     <row r="117" spans="1:8">
       <c r="A117" s="7"/>
       <c r="B117" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F117" s="8"/>
       <c r="G117" s="10"/>
@@ -8350,14 +8344,14 @@
     <row r="118" spans="1:8">
       <c r="A118" s="7"/>
       <c r="B118" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F118" s="8"/>
       <c r="G118" s="10"/>
@@ -8366,19 +8360,19 @@
     <row r="119" spans="1:8">
       <c r="A119" s="7"/>
       <c r="B119" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="E119" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="C119" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D119" s="8" t="s">
+      <c r="F119" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>425</v>
       </c>
       <c r="G119" s="10">
         <v>1</v>
@@ -8388,19 +8382,19 @@
     <row r="120" spans="1:8">
       <c r="A120" s="7"/>
       <c r="B120" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E120" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="C120" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D120" s="8" t="s">
+      <c r="F120" s="8" t="s">
         <v>427</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>429</v>
       </c>
       <c r="G120" s="10">
         <v>1</v>
@@ -8410,19 +8404,19 @@
     <row r="121" spans="1:8">
       <c r="A121" s="7"/>
       <c r="B121" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E121" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="C121" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D121" s="8" t="s">
+      <c r="F121" s="8" t="s">
         <v>431</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="G121" s="10">
         <v>1</v>
@@ -8432,19 +8426,19 @@
     <row r="122" spans="1:8">
       <c r="A122" s="7"/>
       <c r="B122" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="E122" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="C122" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D122" s="8" t="s">
+      <c r="F122" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>437</v>
       </c>
       <c r="G122" s="10">
         <v>1</v>
@@ -8453,16 +8447,16 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
@@ -8472,13 +8466,13 @@
     <row r="124" spans="1:8">
       <c r="A124" s="7"/>
       <c r="B124" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C124" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
@@ -8488,13 +8482,13 @@
     <row r="125" spans="1:8">
       <c r="A125" s="7"/>
       <c r="B125" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
@@ -8504,13 +8498,13 @@
     <row r="126" spans="1:8">
       <c r="A126" s="7"/>
       <c r="B126" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C126" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
@@ -8520,17 +8514,17 @@
     <row r="127" spans="1:8">
       <c r="A127" s="7"/>
       <c r="B127" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G127" s="10" t="s">
         <v>22</v>
@@ -8539,7 +8533,7 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B128" s="8" t="s">
         <v>19</v>
@@ -8548,7 +8542,7 @@
         <v>28</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
@@ -8574,13 +8568,13 @@
     <row r="130" spans="1:8">
       <c r="A130" s="7"/>
       <c r="B130" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
@@ -8590,13 +8584,13 @@
     <row r="131" spans="1:8">
       <c r="A131" s="7"/>
       <c r="B131" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C131" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
@@ -8605,16 +8599,16 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C132" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
@@ -8624,13 +8618,13 @@
     <row r="133" spans="1:8">
       <c r="A133" s="15"/>
       <c r="B133" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C133" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
@@ -8640,13 +8634,13 @@
     <row r="134" spans="1:8">
       <c r="A134" s="15"/>
       <c r="B134" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
@@ -8656,13 +8650,13 @@
     <row r="135" spans="1:8">
       <c r="A135" s="15"/>
       <c r="B135" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C135" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
@@ -8672,13 +8666,13 @@
     <row r="136" spans="1:8">
       <c r="A136" s="15"/>
       <c r="B136" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
@@ -8688,13 +8682,13 @@
     <row r="137" spans="1:8">
       <c r="A137" s="15"/>
       <c r="B137" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C137" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
@@ -8704,13 +8698,13 @@
     <row r="138" spans="1:8">
       <c r="A138" s="15"/>
       <c r="B138" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
@@ -8720,13 +8714,13 @@
     <row r="139" spans="1:8">
       <c r="A139" s="15"/>
       <c r="B139" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C139" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
@@ -8736,13 +8730,13 @@
     <row r="140" spans="1:8">
       <c r="A140" s="15"/>
       <c r="B140" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
@@ -8752,13 +8746,13 @@
     <row r="141" spans="1:8">
       <c r="A141" s="15"/>
       <c r="B141" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C141" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
@@ -8768,13 +8762,13 @@
     <row r="142" spans="1:8">
       <c r="A142" s="15"/>
       <c r="B142" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
@@ -8784,13 +8778,13 @@
     <row r="143" spans="1:8">
       <c r="A143" s="15"/>
       <c r="B143" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
@@ -8800,13 +8794,13 @@
     <row r="144" spans="1:8">
       <c r="A144" s="15"/>
       <c r="B144" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
@@ -8816,13 +8810,13 @@
     <row r="145" spans="1:8">
       <c r="A145" s="15"/>
       <c r="B145" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C145" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
@@ -8832,13 +8826,13 @@
     <row r="146" spans="1:8">
       <c r="A146" s="15"/>
       <c r="B146" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
@@ -8848,13 +8842,13 @@
     <row r="147" spans="1:8">
       <c r="A147" s="15"/>
       <c r="B147" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C147" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
@@ -8864,13 +8858,13 @@
     <row r="148" spans="1:8">
       <c r="A148" s="15"/>
       <c r="B148" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
@@ -8880,13 +8874,13 @@
     <row r="149" spans="1:8">
       <c r="A149" s="15"/>
       <c r="B149" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
@@ -8896,13 +8890,13 @@
     <row r="150" spans="1:8">
       <c r="A150" s="15"/>
       <c r="B150" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
@@ -8912,13 +8906,13 @@
     <row r="151" spans="1:8">
       <c r="A151" s="15"/>
       <c r="B151" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C151" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
@@ -8928,13 +8922,13 @@
     <row r="152" spans="1:8">
       <c r="A152" s="15"/>
       <c r="B152" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C152" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
@@ -8944,13 +8938,13 @@
     <row r="153" spans="1:8">
       <c r="A153" s="15"/>
       <c r="B153" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C153" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
@@ -8960,13 +8954,13 @@
     <row r="154" spans="1:8">
       <c r="A154" s="15"/>
       <c r="B154" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C154" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
@@ -8976,13 +8970,13 @@
     <row r="155" spans="1:8">
       <c r="A155" s="15"/>
       <c r="B155" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C155" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
@@ -8992,13 +8986,13 @@
     <row r="156" spans="1:8">
       <c r="A156" s="15"/>
       <c r="B156" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C156" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E156"/>
       <c r="F156" s="8"/>
@@ -9008,13 +9002,13 @@
     <row r="157" spans="1:8">
       <c r="A157" s="15"/>
       <c r="B157" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C157" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E157"/>
       <c r="F157" s="8"/>
@@ -9024,13 +9018,13 @@
     <row r="158" spans="1:8">
       <c r="A158" s="15"/>
       <c r="B158" s="12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C158" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
@@ -9040,13 +9034,13 @@
     <row r="159" spans="1:8">
       <c r="A159" s="15"/>
       <c r="B159" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C159" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
@@ -9056,14 +9050,14 @@
     <row r="160" spans="1:8">
       <c r="A160" s="15"/>
       <c r="B160" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="10"/>
@@ -9072,14 +9066,14 @@
     <row r="161" spans="1:8">
       <c r="A161" s="15"/>
       <c r="B161" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F161" s="8"/>
       <c r="G161" s="10"/>
@@ -9088,14 +9082,14 @@
     <row r="162" spans="1:8">
       <c r="A162" s="15"/>
       <c r="B162" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="10"/>
@@ -9104,14 +9098,14 @@
     <row r="163" spans="1:8">
       <c r="A163" s="15"/>
       <c r="B163" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="10"/>
@@ -9120,14 +9114,14 @@
     <row r="164" spans="1:8">
       <c r="A164" s="15"/>
       <c r="B164" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="10"/>
@@ -9136,14 +9130,14 @@
     <row r="165" spans="1:8">
       <c r="A165" s="15"/>
       <c r="B165" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="10"/>
@@ -9152,14 +9146,14 @@
     <row r="166" spans="1:8">
       <c r="A166" s="15"/>
       <c r="B166" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="10"/>
@@ -9168,14 +9162,14 @@
     <row r="167" spans="1:8">
       <c r="A167" s="15"/>
       <c r="B167" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="10"/>
@@ -9184,14 +9178,14 @@
     <row r="168" spans="1:8">
       <c r="A168" s="15"/>
       <c r="B168" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="10"/>
@@ -9200,14 +9194,14 @@
     <row r="169" spans="1:8">
       <c r="A169" s="15"/>
       <c r="B169" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="10"/>
@@ -9216,14 +9210,14 @@
     <row r="170" spans="1:8">
       <c r="A170" s="15"/>
       <c r="B170" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="10"/>
@@ -9232,14 +9226,14 @@
     <row r="171" spans="1:8">
       <c r="A171" s="15"/>
       <c r="B171" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="10"/>
@@ -9248,14 +9242,14 @@
     <row r="172" spans="1:8">
       <c r="A172" s="15"/>
       <c r="B172" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="10"/>
@@ -9264,14 +9258,14 @@
     <row r="173" spans="1:8">
       <c r="A173" s="15"/>
       <c r="B173" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F173" s="8"/>
       <c r="G173" s="10"/>
@@ -9280,14 +9274,14 @@
     <row r="174" spans="1:8">
       <c r="A174" s="15"/>
       <c r="B174" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F174" s="8"/>
       <c r="G174" s="10"/>
@@ -9296,14 +9290,14 @@
     <row r="175" spans="1:8">
       <c r="A175" s="15"/>
       <c r="B175" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F175" s="8"/>
       <c r="G175" s="10"/>
@@ -9312,14 +9306,14 @@
     <row r="176" spans="1:8">
       <c r="A176" s="15"/>
       <c r="B176" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F176" s="8"/>
       <c r="G176" s="10"/>
@@ -9328,14 +9322,14 @@
     <row r="177" spans="1:8">
       <c r="A177" s="15"/>
       <c r="B177" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D177" s="8"/>
       <c r="E177" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F177" s="8"/>
       <c r="G177" s="10"/>
@@ -9344,14 +9338,14 @@
     <row r="178" spans="1:8">
       <c r="A178" s="15"/>
       <c r="B178" s="12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D178" s="8"/>
       <c r="E178" s="12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F178" s="8"/>
       <c r="G178" s="10"/>
@@ -9360,14 +9354,14 @@
     <row r="179" spans="1:8">
       <c r="A179" s="15"/>
       <c r="B179" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D179" s="8"/>
       <c r="E179" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F179" s="8"/>
       <c r="G179" s="10"/>
@@ -9376,14 +9370,14 @@
     <row r="180" spans="1:8">
       <c r="A180" s="15"/>
       <c r="B180" s="12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D180" s="8"/>
       <c r="E180" s="12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F180" s="8"/>
       <c r="G180" s="10"/>
@@ -9392,14 +9386,14 @@
     <row r="181" spans="1:8">
       <c r="A181" s="15"/>
       <c r="B181" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D181" s="8"/>
       <c r="E181" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F181" s="8"/>
       <c r="G181" s="10"/>
@@ -9408,14 +9402,14 @@
     <row r="182" spans="1:8">
       <c r="A182" s="15"/>
       <c r="B182" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D182" s="8"/>
       <c r="E182" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F182" s="8"/>
       <c r="G182" s="10"/>
@@ -9424,14 +9418,14 @@
     <row r="183" spans="1:8">
       <c r="A183" s="15"/>
       <c r="B183" s="12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D183" s="8"/>
       <c r="E183" s="12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F183" s="8"/>
       <c r="G183" s="10"/>
@@ -9440,14 +9434,14 @@
     <row r="184" spans="1:8">
       <c r="A184" s="15"/>
       <c r="B184" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D184" s="8"/>
       <c r="E184" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F184" s="8"/>
       <c r="G184" s="10"/>
@@ -9456,14 +9450,14 @@
     <row r="185" spans="1:8">
       <c r="A185" s="15"/>
       <c r="B185" s="12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D185" s="8"/>
       <c r="E185" s="12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F185" s="8"/>
       <c r="G185" s="10"/>
